--- a/Compititor's_Price/Core-Products_Prices/Core-Products_Prices_03-06-2026.xlsx
+++ b/Compititor's_Price/Core-Products_Prices/Core-Products_Prices_03-06-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Core-Products_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D2347CB-F921-4100-8DDE-7E613AC7E802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBAC3CE1-40D5-48F8-A506-19CA07607055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3690" yWindow="2715" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33990" yWindow="270" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
